--- a/Analysis/Sensitivity_merec_entropy_arms_qwen.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_qwen.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -502,10 +502,10 @@
         <v>0.6793199999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22962</v>
+        <v>0.20636</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9253199999999999</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.27112</v>
+        <v>0.24786</v>
       </c>
       <c r="F3" t="n">
-        <v>0.28822</v>
+        <v>0.2640999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5118</v>
+        <v>0.4995</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7774</v>
+        <v>0.77844</v>
       </c>
       <c r="I3" t="n">
-        <v>0.22962</v>
+        <v>0.20636</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9253199999999999</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9253199999999999</v>
+        <v>0.9212</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9352599999999999</v>
+        <v>0.9337</v>
       </c>
       <c r="G4" t="n">
-        <v>0.92394</v>
+        <v>0.92188</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9886800000000001</v>
+        <v>0.99382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22962</v>
+        <v>0.20636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9253199999999999</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +601,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-0.005100000000000001</v>
+        <v>-0.006460000000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0164</v>
+        <v>-0.01796</v>
       </c>
       <c r="G5" t="n">
-        <v>0.30426</v>
+        <v>0.30324</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6813800000000001</v>
+        <v>0.6793199999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.21946</v>
+        <v>0.2263</v>
       </c>
       <c r="J5" t="n">
-        <v>0.88764</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.21436</v>
+        <v>0.21984</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2292</v>
+        <v>0.23642</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4554</v>
+        <v>0.46258</v>
       </c>
       <c r="H6" t="n">
-        <v>0.76102</v>
+        <v>0.78462</v>
       </c>
       <c r="I6" t="n">
-        <v>0.21946</v>
+        <v>0.2263</v>
       </c>
       <c r="J6" t="n">
-        <v>0.88764</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="7">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.88764</v>
+        <v>0.889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9013200000000001</v>
+        <v>0.90234</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9311400000000001</v>
+        <v>0.93216</v>
       </c>
       <c r="H7" t="n">
-        <v>0.98254</v>
+        <v>0.98356</v>
       </c>
       <c r="I7" t="n">
-        <v>0.21946</v>
+        <v>0.2263</v>
       </c>
       <c r="J7" t="n">
-        <v>0.88764</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="8">
@@ -742,7 +742,7 @@
         <v>0.67728</v>
       </c>
       <c r="I8" t="n">
-        <v>0.21874</v>
+        <v>0.2201</v>
       </c>
       <c r="J8" t="n">
         <v>0.9219200000000001</v>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.22396</v>
+        <v>0.22532</v>
       </c>
       <c r="F9" t="n">
-        <v>0.23896</v>
+        <v>0.24102</v>
       </c>
       <c r="G9" t="n">
-        <v>0.48818</v>
+        <v>0.4841</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7723</v>
+        <v>0.7846</v>
       </c>
       <c r="I9" t="n">
-        <v>0.21874</v>
+        <v>0.2201</v>
       </c>
       <c r="J9" t="n">
         <v>0.9219200000000001</v>
@@ -822,7 +822,7 @@
         <v>0.97944</v>
       </c>
       <c r="I10" t="n">
-        <v>0.21874</v>
+        <v>0.2201</v>
       </c>
       <c r="J10" t="n">
         <v>0.9219200000000001</v>
@@ -862,7 +862,7 @@
         <v>0.6978</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1886</v>
+        <v>0.18994</v>
       </c>
       <c r="J11" t="n">
         <v>0.90344</v>
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.25952</v>
+        <v>0.26086</v>
       </c>
       <c r="F12" t="n">
-        <v>0.27744</v>
+        <v>0.2794800000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.49642</v>
+        <v>0.4922800000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.76512</v>
+        <v>0.7774599999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1886</v>
+        <v>0.18994</v>
       </c>
       <c r="J12" t="n">
         <v>0.90344</v>
@@ -942,7 +942,7 @@
         <v>0.97536</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1886</v>
+        <v>0.18994</v>
       </c>
       <c r="J13" t="n">
         <v>0.90344</v>
@@ -982,10 +982,10 @@
         <v>0.65778</v>
       </c>
       <c r="I14" t="n">
-        <v>0.21398</v>
+        <v>0.18734</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8609399999999999</v>
+        <v>0.85684</v>
       </c>
     </row>
     <row r="15">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.19794</v>
+        <v>0.1713</v>
       </c>
       <c r="F15" t="n">
-        <v>0.21436</v>
+        <v>0.18616</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4636</v>
+        <v>0.45026</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7723000000000001</v>
+        <v>0.7712600000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.21398</v>
+        <v>0.18734</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8609399999999999</v>
+        <v>0.85684</v>
       </c>
     </row>
     <row r="16">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8609399999999999</v>
+        <v>0.85684</v>
       </c>
       <c r="F16" t="n">
-        <v>0.87514</v>
+        <v>0.87102</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8633200000000001</v>
+        <v>0.86126</v>
       </c>
       <c r="H16" t="n">
         <v>0.97226</v>
       </c>
       <c r="I16" t="n">
-        <v>0.21398</v>
+        <v>0.18734</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8609399999999999</v>
+        <v>0.85684</v>
       </c>
     </row>
     <row r="17">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-0.005100000000000001</v>
+        <v>-0.007179999999999997</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0164</v>
+        <v>-0.01796</v>
       </c>
       <c r="G17" t="n">
-        <v>0.30426</v>
+        <v>0.30116</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6813800000000001</v>
+        <v>0.68136</v>
       </c>
       <c r="I17" t="n">
-        <v>0.22014</v>
+        <v>0.22564</v>
       </c>
       <c r="J17" t="n">
-        <v>0.88764</v>
+        <v>0.88558</v>
       </c>
     </row>
     <row r="18">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.21504</v>
+        <v>0.21846</v>
       </c>
       <c r="F18" t="n">
-        <v>0.23026</v>
+        <v>0.23538</v>
       </c>
       <c r="G18" t="n">
-        <v>0.45438</v>
+        <v>0.4605399999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7630800000000001</v>
+        <v>0.7846200000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22014</v>
+        <v>0.22564</v>
       </c>
       <c r="J18" t="n">
-        <v>0.88764</v>
+        <v>0.88558</v>
       </c>
     </row>
     <row r="19">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.88764</v>
+        <v>0.88558</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9013200000000001</v>
+        <v>0.89984</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9311400000000001</v>
+        <v>0.9270400000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.98254</v>
+        <v>0.98356</v>
       </c>
       <c r="I19" t="n">
-        <v>0.22014</v>
+        <v>0.22564</v>
       </c>
       <c r="J19" t="n">
-        <v>0.88764</v>
+        <v>0.88558</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Sensitivity_merec_entropy_arms_qwen.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_qwen.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-0.01604</v>
+        <v>-0.0147</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.021</v>
+        <v>-0.01948</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2981</v>
+        <v>0.30012</v>
       </c>
       <c r="H14" t="n">
-        <v>0.65778</v>
+        <v>0.65878</v>
       </c>
       <c r="I14" t="n">
-        <v>0.18734</v>
+        <v>0.1928</v>
       </c>
       <c r="J14" t="n">
-        <v>0.85684</v>
+        <v>0.8561400000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.1713</v>
+        <v>0.1781</v>
       </c>
       <c r="F15" t="n">
-        <v>0.18616</v>
+        <v>0.19178</v>
       </c>
       <c r="G15" t="n">
-        <v>0.45026</v>
+        <v>0.45436</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7712600000000001</v>
+        <v>0.77744</v>
       </c>
       <c r="I15" t="n">
-        <v>0.18734</v>
+        <v>0.1928</v>
       </c>
       <c r="J15" t="n">
-        <v>0.85684</v>
+        <v>0.8561400000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.85684</v>
+        <v>0.8561400000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.87102</v>
+        <v>0.8731</v>
       </c>
       <c r="G16" t="n">
-        <v>0.86126</v>
+        <v>0.85512</v>
       </c>
       <c r="H16" t="n">
-        <v>0.97226</v>
+        <v>0.9773999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.18734</v>
+        <v>0.1928</v>
       </c>
       <c r="J16" t="n">
-        <v>0.85684</v>
+        <v>0.8561400000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-0.007179999999999997</v>
+        <v>-0.006460000000000002</v>
       </c>
       <c r="F17" t="n">
         <v>-0.01796</v>
       </c>
       <c r="G17" t="n">
-        <v>0.30116</v>
+        <v>0.30324</v>
       </c>
       <c r="H17" t="n">
-        <v>0.68136</v>
+        <v>0.6793199999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.22564</v>
+        <v>0.2263</v>
       </c>
       <c r="J17" t="n">
-        <v>0.88558</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="18">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.21846</v>
+        <v>0.21984</v>
       </c>
       <c r="F18" t="n">
-        <v>0.23538</v>
+        <v>0.23642</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4605399999999999</v>
+        <v>0.46258</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7846200000000001</v>
+        <v>0.78462</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22564</v>
+        <v>0.2263</v>
       </c>
       <c r="J18" t="n">
-        <v>0.88558</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="19">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.88558</v>
+        <v>0.889</v>
       </c>
       <c r="F19" t="n">
-        <v>0.89984</v>
+        <v>0.90234</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9270400000000001</v>
+        <v>0.93216</v>
       </c>
       <c r="H19" t="n">
         <v>0.98356</v>
       </c>
       <c r="I19" t="n">
-        <v>0.22564</v>
+        <v>0.2263</v>
       </c>
       <c r="J19" t="n">
-        <v>0.88558</v>
+        <v>0.889</v>
       </c>
     </row>
   </sheetData>
